--- a/excel/PCL_01_Sources.xlsx
+++ b/excel/PCL_01_Sources.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Source_Reference_Long!$A$1:$L$482</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1" iterate="false" refMode="A1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">Impairments, segment note, production</t>
   </si>
   <si>
-    <t xml:space="preserve">Page locations not yet mapped (file 14.7 MB; could not be parsed remotely).</t>
+    <t xml:space="preserve">Read in full in Oct 2026 (official PDF text layer): automotive EBITDA table PDF p.99; segment reporting table PDF p.153 (printed pp.304-305) gives automotive impairment losses FY2023 = 2.</t>
   </si>
   <si>
     <t xml:space="preserve">S005</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">2024_FY_AnnualReport.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Page locations not yet mapped (17 MB).</t>
+    <t xml:space="preserve">Read in full in Oct 2026 (official PDF text layer): automotive EBITDA table PDF p.70; segment reporting table PDF p.189 gives automotive impairment losses FY2024 = 3.</t>
   </si>
   <si>
     <t xml:space="preserve">S009</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">Segment note (TOC p.350), income statement (TOC p.320), impairments</t>
   </si>
   <si>
-    <t xml:space="preserve">Too large to parse remotely; pages from table of contents only.</t>
+    <t xml:space="preserve">Read in full in Oct 2026 (official PDF text layer): segment reporting table PDF p.176 gives automotive impairment losses FY2025 = 1,195; no realignment provision release for FY2025 is stated.</t>
   </si>
   <si>
     <t xml:space="preserve">S013</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">FY2023/FY2024 automotive and FS figures in EUR m</t>
   </si>
   <si>
-    <t xml:space="preserve">Added in Phase 2 to replace unparseable S004/S008 PDFs for segment figures. Cite by section heading.</t>
+    <t xml:space="preserve">Added in Phase 2 to replace unparseable S004/S008 PDFs for segment figures. Cite by section heading. Link check Oct 2026: this URL now redirects to the 2025 report landing page. The same FY2023/FY2024 figures are printed in the official PDF annual reports S004 and S008 (verified).</t>
   </si>
   <si>
     <t xml:space="preserve">Var_ID</t>
@@ -4503,7 +4503,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
